--- a/DataTables/DetailText/剧情/014_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/014_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BDBC73-4906-44A5-9810-F3D942D4E333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F206CB-CB97-4074-904D-0723AA34F18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -75,9 +75,6 @@
     <t>SortIndex</t>
   </si>
   <si>
-    <t>clinic</t>
-  </si>
-  <si>
     <t>current_scene</t>
   </si>
   <si>
@@ -207,9 +204,6 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
     <t>shen_xiu_wen</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -251,6 +245,14 @@
     <t>014治疗失败</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>failed</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>clinic</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -260,7 +262,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -274,7 +276,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -295,7 +297,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -398,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -433,9 +435,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -462,24 +461,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -758,130 +745,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:20" s="21" customFormat="1">
+      <c r="A1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="J1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="K1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="S1" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="36">
+      <c r="A2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="22" customFormat="1" ht="36">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="24" t="s">
+      <c r="N2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="14" t="s">
+      <c r="O2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="26" t="b">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T2" s="25"/>
+      <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20">
       <c r="C3" s="9"/>
       <c r="H3" s="11"/>
-      <c r="L3" s="13"/>
+      <c r="L3" s="12"/>
       <c r="O3" s="10"/>
     </row>
     <row r="4" spans="1:20">
@@ -967,14 +954,14 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.3984375" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1003,8 +990,8 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="27" t="s">
-        <v>40</v>
+      <c r="I1" s="22" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1014,19 +1001,19 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>13</v>
+      <c r="C2" s="13" t="s">
+        <v>12</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1"/>
     </row>
